--- a/modules/consulta/descargas/base_consulta.xlsx
+++ b/modules/consulta/descargas/base_consulta.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -501,6 +501,142 @@
       <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>last_update</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1005259871</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Andrea del Pilar Guerrero Delgado</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>22</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>F · Femenino</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3 · Hijo(a)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2 · Indígena</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2 · No requiere asistencia médica</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1 · Contributivo</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2 · No habitable</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Propia</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>PER-20260815-CJVP4L-P01</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>PER-20260815-CJVP4L</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>HOG-20260815-UW466</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>matched_hogar</t>
+        </is>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Cll 18 # 121-159, A, Apartamento 1001</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Madera</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>VIV-20260815-4JRZYX</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>personas_hoja.csv</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-15T12:48:39</t>
         </is>
       </c>
     </row>
@@ -511,7 +647,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -583,6 +719,62 @@
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>direccion_completa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PER-20260815-CJVP4L</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HOG-20260815-UW466</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>matched_hogar</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>id_hogar</t>
+        </is>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>VIV-20260815-4JRZYX</t>
+        </is>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>personas_hoja.csv</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-08-15T12:48:39</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Cll 18 # 121-159, A, Apartamento 1001</t>
         </is>
       </c>
     </row>
@@ -593,7 +785,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -700,6 +892,87 @@
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>last_update</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>VIV-20260815-4JRZYX</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HOG-20260815-UW466</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Andrea del Pilar Guerrero Delgado</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1005259871</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1005259871</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Madera</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Conjunto residencial</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Cll 18 # 121-159, A, Apartamento 1001</t>
+        </is>
+      </c>
+      <c r="N2">
+        <v>3.34534</v>
+      </c>
+      <c r="O2">
+        <v>-76.53081</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>viviendas_hoja.csv</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-08-15T12:48:39</t>
         </is>
       </c>
     </row>
@@ -710,7 +983,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -862,6 +1135,122 @@
       <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>last_update</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AFE-20260815-BXEUSE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bochalema </t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Cll 43 # 109-78, Unidad Residencial Porto Alegre 1, J, Apartamento 504</t>
+        </is>
+      </c>
+      <c r="G2">
+        <v>3.358</v>
+      </c>
+      <c r="H2">
+        <v>-76.519262</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Se encuentra bien</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>No aplica (sin riesgo)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Conjunto Residencial</t>
+        </is>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Todo esta bien</t>
+        </is>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Captura de pantalla 2026-08-05 133044.jpg</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1RI8voHTKzecLdO2jiR2D4FYL0t0XArEx/view</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Claudia Rincón</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Alcaldia de Cali</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>afectaciones_hoja.csv</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2026-08-15T12:48:39</t>
         </is>
       </c>
     </row>
